--- a/复试/找调剂/磁场转动.xlsx
+++ b/复试/找调剂/磁场转动.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="208">
   <si>
     <t>日期</t>
   </si>
@@ -249,6 +249,9 @@
   </si>
   <si>
     <t>还差</t>
+  </si>
+  <si>
+    <t>总差</t>
   </si>
   <si>
     <t>偏置甄别</t>
@@ -5558,7 +5561,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" hidden="1" spans="1:72">
+    <row r="81" hidden="1" spans="1:73">
       <c r="A81" s="1" t="s">
         <v>66</v>
       </c>
@@ -5596,7 +5599,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="82" hidden="1" spans="1:72">
+    <row r="82" hidden="1" spans="1:73">
       <c r="A82" s="1" t="s">
         <v>67</v>
       </c>
@@ -5634,12 +5637,12 @@
         <v>290</v>
       </c>
     </row>
-    <row r="84" spans="1:72">
+    <row r="84" spans="1:73">
       <c r="A84" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="85" spans="1:72">
+    <row r="85" spans="1:73">
       <c r="A85" s="1" t="s">
         <v>7</v>
       </c>
@@ -5679,10 +5682,13 @@
       <c r="BQ85" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="86" spans="1:72">
+      <c r="BT85" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="86" spans="1:73">
       <c r="A86" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B86" s="1">
         <v>49</v>
@@ -5784,23 +5790,27 @@
         <f t="shared" ref="BQ86:BQ93" si="34">D86-G86</f>
         <v>0</v>
       </c>
-      <c r="BT86" s="28" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="87" spans="1:72">
+      <c r="BT86" s="1">
+        <f t="shared" ref="BT86:BT93" si="35">B86-J86</f>
+        <v>8</v>
+      </c>
+      <c r="BU86" s="28" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="87" spans="1:73">
       <c r="A87" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B87" s="1">
         <v>74</v>
       </c>
       <c r="C87" s="23">
-        <f t="shared" ref="C87:C95" si="35">4/26</f>
+        <f t="shared" ref="C87:C95" si="36">4/26</f>
         <v>0.153846153846154</v>
       </c>
       <c r="D87" s="1">
-        <f t="shared" ref="D87:D95" si="36">ROUND(B87*C87,0)</f>
+        <f t="shared" ref="D87:D95" si="37">ROUND(B87*C87,0)</f>
         <v>11</v>
       </c>
       <c r="E87" s="23">
@@ -5808,22 +5818,22 @@
         <v>0.0883894098179813</v>
       </c>
       <c r="F87" s="23">
-        <f t="shared" ref="F87:F95" si="37">G87/B87</f>
+        <f t="shared" ref="F87:F95" si="38">G87/B87</f>
         <v>0.0135135135135135</v>
       </c>
       <c r="G87" s="1">
-        <f t="shared" ref="G87:G95" si="38">I87-H87</f>
+        <f t="shared" ref="G87:G95" si="39">I87-H87</f>
         <v>1</v>
       </c>
       <c r="H87" s="1">
         <v>44</v>
       </c>
       <c r="I87" s="21">
-        <f t="shared" ref="I87:I95" si="39">MIN($J$85*D87,J87)</f>
+        <f t="shared" ref="I87:I95" si="40">MIN($J$85*D87,J87)</f>
         <v>45</v>
       </c>
       <c r="J87" s="25">
-        <f t="shared" ref="J87:J95" si="40">BO87+BP87</f>
+        <f t="shared" ref="J87:J95" si="41">BO87+BP87</f>
         <v>45</v>
       </c>
       <c r="K87" s="25"/>
@@ -5892,23 +5902,27 @@
         <f t="shared" si="34"/>
         <v>10</v>
       </c>
-      <c r="BT87" s="28" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="88" spans="1:72">
+      <c r="BT87" s="1">
+        <f t="shared" si="35"/>
+        <v>29</v>
+      </c>
+      <c r="BU87" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="88" spans="1:73">
       <c r="A88" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B88" s="1">
         <v>49</v>
       </c>
       <c r="C88" s="23">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.153846153846154</v>
       </c>
       <c r="D88" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>8</v>
       </c>
       <c r="E88" s="23">
@@ -5916,22 +5930,22 @@
         <v>0.11334804191947</v>
       </c>
       <c r="F88" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.163265306122449</v>
       </c>
       <c r="G88" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>8</v>
       </c>
       <c r="H88" s="1">
         <v>32</v>
       </c>
       <c r="I88" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>40</v>
       </c>
       <c r="J88" s="21">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>41</v>
       </c>
       <c r="K88" s="21"/>
@@ -6000,23 +6014,27 @@
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="BT88" s="28" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="89" spans="1:72">
+      <c r="BT88" s="1">
+        <f t="shared" si="35"/>
+        <v>8</v>
+      </c>
+      <c r="BU88" s="28" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="89" spans="1:73">
       <c r="A89" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B89" s="1">
         <v>12</v>
       </c>
       <c r="C89" s="23">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.153846153846154</v>
       </c>
       <c r="D89" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>2</v>
       </c>
       <c r="E89" s="23">
@@ -6024,22 +6042,22 @@
         <v>0.12667769810627</v>
       </c>
       <c r="F89" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.166666666666667</v>
       </c>
       <c r="G89" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2</v>
       </c>
       <c r="H89" s="1">
         <v>8</v>
       </c>
       <c r="I89" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>10</v>
       </c>
       <c r="J89" s="21">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>11</v>
       </c>
       <c r="K89" s="21"/>
@@ -6108,23 +6126,27 @@
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="BT89" s="28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="90" spans="1:72">
+      <c r="BT89" s="1">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="BU89" s="28" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="90" spans="1:73">
       <c r="A90" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B90" s="1">
         <v>92</v>
       </c>
       <c r="C90" s="23">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.153846153846154</v>
       </c>
       <c r="D90" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>14</v>
       </c>
       <c r="E90" s="23">
@@ -6132,22 +6154,22 @@
         <v>0.105689984571972</v>
       </c>
       <c r="F90" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.0217391304347826</v>
       </c>
       <c r="G90" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2</v>
       </c>
       <c r="H90" s="1">
         <v>56</v>
       </c>
       <c r="I90" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>58</v>
       </c>
       <c r="J90" s="25">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>58</v>
       </c>
       <c r="K90" s="25"/>
@@ -6216,23 +6238,27 @@
         <f t="shared" si="34"/>
         <v>12</v>
       </c>
-      <c r="BT90" s="28" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="91" spans="1:72">
+      <c r="BT90" s="1">
+        <f t="shared" si="35"/>
+        <v>34</v>
+      </c>
+      <c r="BU90" s="28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="91" spans="1:73">
       <c r="A91" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B91" s="1">
         <v>51</v>
       </c>
       <c r="C91" s="23">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.153846153846154</v>
       </c>
       <c r="D91" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>8</v>
       </c>
       <c r="E91" s="23">
@@ -6240,22 +6266,22 @@
         <v>0.114218777992983</v>
       </c>
       <c r="F91" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.156862745098039</v>
       </c>
       <c r="G91" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>8</v>
       </c>
       <c r="H91" s="1">
         <v>32</v>
       </c>
       <c r="I91" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>40</v>
       </c>
       <c r="J91" s="21">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>41</v>
       </c>
       <c r="K91" s="21"/>
@@ -6324,23 +6350,27 @@
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="BT91" s="28" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="92" spans="1:72">
+      <c r="BT91" s="1">
+        <f t="shared" si="35"/>
+        <v>10</v>
+      </c>
+      <c r="BU91" s="28" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="92" spans="1:73">
       <c r="A92" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B92" s="1">
         <v>74</v>
       </c>
       <c r="C92" s="23">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.153846153846154</v>
       </c>
       <c r="D92" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>11</v>
       </c>
       <c r="E92" s="23">
@@ -6348,22 +6378,22 @@
         <v>0.0998323116387733</v>
       </c>
       <c r="F92" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.0135135135135135</v>
       </c>
       <c r="G92" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1</v>
       </c>
       <c r="H92" s="1">
         <v>44</v>
       </c>
       <c r="I92" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>45</v>
       </c>
       <c r="J92" s="25">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>45</v>
       </c>
       <c r="K92" s="25"/>
@@ -6432,23 +6462,27 @@
         <f t="shared" si="34"/>
         <v>10</v>
       </c>
-      <c r="BT92" s="28" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="93" spans="1:72">
+      <c r="BT92" s="1">
+        <f t="shared" si="35"/>
+        <v>29</v>
+      </c>
+      <c r="BU92" s="28" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="93" spans="1:73">
       <c r="A93" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B93" s="1">
         <v>60</v>
       </c>
       <c r="C93" s="23">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.153846153846154</v>
       </c>
       <c r="D93" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>9</v>
       </c>
       <c r="E93" s="23">
@@ -6456,22 +6490,22 @@
         <v>0.106103272683927</v>
       </c>
       <c r="F93" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.15</v>
       </c>
       <c r="G93" s="1">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>9</v>
       </c>
       <c r="H93" s="1">
         <v>36</v>
       </c>
       <c r="I93" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>45</v>
       </c>
       <c r="J93" s="21">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>46</v>
       </c>
       <c r="K93" s="21"/>
@@ -6540,16 +6574,20 @@
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="BT93" s="28" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="95" spans="1:72">
+      <c r="BT93" s="1">
+        <f t="shared" si="35"/>
+        <v>14</v>
+      </c>
+      <c r="BU93" s="28" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="95" spans="1:73">
       <c r="A95" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="96" spans="1:72">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="96" spans="1:73">
       <c r="A96" s="1" t="s">
         <v>7</v>
       </c>
@@ -6583,17 +6621,17 @@
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B97" s="1">
         <v>372</v>
       </c>
       <c r="C97" s="23">
-        <f t="shared" ref="C97:C100" si="41">4/26</f>
+        <f t="shared" ref="C97:C100" si="42">4/26</f>
         <v>0.153846153846154</v>
       </c>
       <c r="D97" s="1">
-        <f t="shared" ref="D97:D100" si="42">ROUND(B97*C97,0)</f>
+        <f t="shared" ref="D97:D100" si="43">ROUND(B97*C97,0)</f>
         <v>57</v>
       </c>
       <c r="E97" s="23">
@@ -6601,18 +6639,18 @@
         <v>0</v>
       </c>
       <c r="F97" s="23">
-        <f t="shared" ref="F97:F100" si="43">G97/B97</f>
+        <f t="shared" ref="F97:F100" si="44">G97/B97</f>
         <v>0</v>
       </c>
       <c r="G97" s="1">
-        <f t="shared" ref="G97:G100" si="44">I97-H97</f>
+        <f t="shared" ref="G97:G100" si="45">I97-H97</f>
         <v>0</v>
       </c>
       <c r="H97" s="1">
         <v>0</v>
       </c>
       <c r="I97" s="21">
-        <f t="shared" ref="I97:I100" si="45">MIN($J$96*D97,J97)</f>
+        <f t="shared" ref="I97:I100" si="46">MIN($J$96*D97,J97)</f>
         <v>0</v>
       </c>
       <c r="J97" s="21">
@@ -6621,17 +6659,17 @@
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B98" s="1">
         <v>290</v>
       </c>
       <c r="C98" s="23">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.153846153846154</v>
       </c>
       <c r="D98" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>45</v>
       </c>
       <c r="E98" s="23">
@@ -6639,18 +6677,18 @@
         <v>0</v>
       </c>
       <c r="F98" s="23">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="G98" s="1">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
+      <c r="G98" s="1">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
       <c r="H98" s="1">
         <v>0</v>
       </c>
       <c r="I98" s="21">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="J98" s="21">
@@ -6659,17 +6697,17 @@
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B99" s="1">
         <v>226</v>
       </c>
       <c r="C99" s="23">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.153846153846154</v>
       </c>
       <c r="D99" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>35</v>
       </c>
       <c r="E99" s="23">
@@ -6677,18 +6715,18 @@
         <v>0</v>
       </c>
       <c r="F99" s="23">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="G99" s="1">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
+      <c r="G99" s="1">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
       <c r="H99" s="1">
         <v>0</v>
       </c>
       <c r="I99" s="21">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="J99" s="21">
@@ -6697,17 +6735,17 @@
     </row>
     <row r="100" spans="1:10">
       <c r="A100" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B100" s="1">
         <v>661</v>
       </c>
       <c r="C100" s="23">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.153846153846154</v>
       </c>
       <c r="D100" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>102</v>
       </c>
       <c r="E100" s="23">
@@ -6715,18 +6753,18 @@
         <v>0</v>
       </c>
       <c r="F100" s="23">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="G100" s="1">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
+      <c r="G100" s="1">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
       <c r="H100" s="1">
         <v>0</v>
       </c>
       <c r="I100" s="21">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="J100" s="21">
@@ -6757,13 +6795,13 @@
         <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" hidden="1" spans="1:5">
@@ -6774,10 +6812,10 @@
         <v>202</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" hidden="1" spans="1:5">
@@ -6788,10 +6826,10 @@
         <v>390</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" hidden="1" spans="1:5">
@@ -6802,10 +6840,10 @@
         <v>484</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" hidden="1" spans="1:5">
@@ -6816,10 +6854,10 @@
         <v>240</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" hidden="1" spans="1:5">
@@ -6830,10 +6868,10 @@
         <v>271</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" hidden="1" spans="1:5">
@@ -6844,18 +6882,18 @@
         <v>278</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" hidden="1" spans="1:5">
       <c r="D8" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" hidden="1" spans="1:5">
@@ -6866,10 +6904,10 @@
         <v>440</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" hidden="1" spans="1:5">
@@ -6880,10 +6918,10 @@
         <v>378</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" hidden="1" spans="1:5">
@@ -6894,10 +6932,10 @@
         <v>209</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" hidden="1" spans="1:5">
@@ -6908,10 +6946,10 @@
         <v>62</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" hidden="1" spans="1:5">
@@ -6922,18 +6960,18 @@
         <v>464</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" hidden="1" spans="1:5">
       <c r="D14" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" hidden="1" spans="1:5">
@@ -6944,10 +6982,10 @@
         <v>132</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" hidden="1" spans="1:5">
@@ -6958,7 +6996,7 @@
         <v>30</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" hidden="1" spans="1:14">
@@ -6969,12 +7007,12 @@
         <v>395</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" hidden="1" spans="1:14">
       <c r="A18" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B18" s="1">
         <v>66</v>
@@ -6982,22 +7020,22 @@
     </row>
     <row r="19" hidden="1" spans="1:14">
       <c r="C19" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" hidden="1" spans="1:14">
@@ -7018,7 +7056,7 @@
         <v>63</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G20" s="1">
         <v>16</v>
@@ -7036,28 +7074,28 @@
         <v>523</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" hidden="1" spans="1:14">
@@ -7068,37 +7106,37 @@
         <v>434</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" hidden="1" spans="1:14">
@@ -7116,66 +7154,66 @@
         <v>83</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" hidden="1" spans="1:14">
       <c r="C25" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" hidden="1" spans="1:14">
@@ -7193,31 +7231,31 @@
         <v>148</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" hidden="1" spans="1:14">
@@ -7228,31 +7266,31 @@
         <v>40</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="28" ht="15.15" hidden="1"/>
@@ -7261,7 +7299,7 @@
         <v>44</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" ht="15.15" hidden="1" spans="1:14">
@@ -7280,10 +7318,10 @@
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H30" s="11"/>
     </row>
@@ -7341,13 +7379,13 @@
         <v>140</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" ht="15.15" hidden="1" spans="1:8">
@@ -7384,10 +7422,10 @@
       </c>
       <c r="E35" s="8"/>
       <c r="F35" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H35" s="8"/>
     </row>
@@ -7407,10 +7445,10 @@
       </c>
       <c r="E36" s="14"/>
       <c r="F36" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H36" s="14"/>
     </row>
@@ -7420,16 +7458,16 @@
         <v>52</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="39" hidden="1" spans="1:8">
@@ -7471,19 +7509,19 @@
         <v>55</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="43" hidden="1" spans="1:8">
@@ -7690,10 +7728,10 @@
         <v>65</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="54" spans="1:6">

--- a/复试/找调剂/磁场转动.xlsx
+++ b/复试/找调剂/磁场转动.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="24000" windowHeight="9720"/>
   </bookViews>
   <sheets>
     <sheet name="进度" sheetId="1" r:id="rId1"/>
@@ -1445,7 +1445,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1532,9 +1532,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -5815,26 +5812,26 @@
       </c>
       <c r="E87" s="23">
         <f>AVERAGE(F$86:F87)</f>
-        <v>0.0883894098179813</v>
+        <v>0.095146166574738</v>
       </c>
       <c r="F87" s="23">
         <f t="shared" ref="F87:F95" si="38">G87/B87</f>
-        <v>0.0135135135135135</v>
+        <v>0.027027027027027</v>
       </c>
       <c r="G87" s="1">
         <f t="shared" ref="G87:G95" si="39">I87-H87</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H87" s="1">
         <v>44</v>
       </c>
       <c r="I87" s="21">
         <f t="shared" ref="I87:I95" si="40">MIN($J$85*D87,J87)</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J87" s="25">
         <f t="shared" ref="J87:J95" si="41">BO87+BP87</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K87" s="25"/>
       <c r="L87" s="25"/>
@@ -5896,15 +5893,15 @@
         <v>13</v>
       </c>
       <c r="BP87" s="25">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BQ87" s="1">
         <f t="shared" si="34"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BT87" s="1">
         <f t="shared" si="35"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BU87" s="28" t="s">
         <v>76</v>
@@ -5927,7 +5924,7 @@
       </c>
       <c r="E88" s="23">
         <f>AVERAGE(F$86:F88)</f>
-        <v>0.11334804191947</v>
+        <v>0.117852546423975</v>
       </c>
       <c r="F88" s="23">
         <f t="shared" si="38"/>
@@ -6039,7 +6036,7 @@
       </c>
       <c r="E89" s="23">
         <f>AVERAGE(F$86:F89)</f>
-        <v>0.12667769810627</v>
+        <v>0.130056076484648</v>
       </c>
       <c r="F89" s="23">
         <f t="shared" si="38"/>
@@ -6151,7 +6148,7 @@
       </c>
       <c r="E90" s="23">
         <f>AVERAGE(F$86:F90)</f>
-        <v>0.105689984571972</v>
+        <v>0.108392687274675</v>
       </c>
       <c r="F90" s="23">
         <f t="shared" si="38"/>
@@ -6263,7 +6260,7 @@
       </c>
       <c r="E91" s="23">
         <f>AVERAGE(F$86:F91)</f>
-        <v>0.114218777992983</v>
+        <v>0.116471030245236</v>
       </c>
       <c r="F91" s="23">
         <f t="shared" si="38"/>
@@ -6375,7 +6372,7 @@
       </c>
       <c r="E92" s="23">
         <f>AVERAGE(F$86:F92)</f>
-        <v>0.0998323116387733</v>
+        <v>0.101762813569275</v>
       </c>
       <c r="F92" s="23">
         <f t="shared" si="38"/>
@@ -6487,7 +6484,7 @@
       </c>
       <c r="E93" s="23">
         <f>AVERAGE(F$86:F93)</f>
-        <v>0.106103272683927</v>
+        <v>0.107792461873116</v>
       </c>
       <c r="F93" s="23">
         <f t="shared" si="38"/>
@@ -6570,7 +6567,7 @@
       <c r="BP93" s="21">
         <v>36</v>
       </c>
-      <c r="BQ93" s="29">
+      <c r="BQ93" s="21">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
@@ -6776,7 +6773,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:BY1 A2:BO2 BY2 A3:BY4 A5:BP6 A7:BY79 A80:I80 K80:BY82 A81:G82 I81:I82" formulaRange="1"/>
+    <ignoredError sqref="I81:I82 A81:G82 K80:BY82 A80:I80 A7:BY79 A5:BP6 A3:BY4 BY2 A2:BO2 A1:BY1" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
